--- a/DuLieuLichSu.xlsx
+++ b/DuLieuLichSu.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9252" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9252"/>
   </bookViews>
   <sheets>
     <sheet name="NhanVat" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3343" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2923" uniqueCount="833">
   <si>
     <t>id</t>
   </si>
@@ -2835,9 +2835,6 @@
     <t>LANH_DAO_DONG_CHI</t>
   </si>
   <si>
-    <t>LANH_DAO_CAP_DUOI</t>
-  </si>
-  <si>
     <t>DONG_CHI_CHI_HUY</t>
   </si>
   <si>
@@ -2859,18 +2856,12 @@
     <t>THAM_MUU_TRUONG_DUOI_QUYEN</t>
   </si>
   <si>
-    <t>BI_LAT_DO</t>
-  </si>
-  <si>
     <t>LANH_DAO_BI_CHONG_DOI</t>
   </si>
   <si>
     <t>PHE_TRUAT</t>
   </si>
   <si>
-    <t>DONG_MINH_LAT_DO</t>
-  </si>
-  <si>
     <t>LANH_DAO_DONG_MINH</t>
   </si>
   <si>
@@ -2880,9 +2871,6 @@
     <t>DOI_THU_CHINH_TRI</t>
   </si>
   <si>
-    <t>HOC_TRO_CU</t>
-  </si>
-  <si>
     <t>CHONG_DOI_CAP_TREN</t>
   </si>
   <si>
@@ -2898,9 +2886,6 @@
     <t>DOI_THU_DAM_PHAN</t>
   </si>
   <si>
-    <t>DONG_CHI_CAP_DUOI</t>
-  </si>
-  <si>
     <t>TIEN_BOI_CACH_MANG</t>
   </si>
   <si>
@@ -2911,9 +2896,6 @@
   </si>
   <si>
     <t>NAM_TRONG</t>
-  </si>
-  <si>
-    <t>DIEN_BIEN_CUA</t>
   </si>
   <si>
     <t>Hồ Chí Minh 1</t>
@@ -2970,6 +2952,9 @@
  - Kết hợp sức mạnh dân tộc với sức mạnh thời đại: Việt Nam đã giữ vững đường lối độc lập, tự chủ, tự lực cánh cường, đồng thời tranh thủ tối đa sự giúp đỡ của Liên Xô, Trung Quốc, các nước xã hội chủ nghĩa, và phong trào phản chiến trên toàn thế giới (kể cả nhân dân Mỹ) để hình thành mặt trận quốc tế bao vây, cô lập kẻ thù.
  - Luôn nêu cao tinh thần cảnh giác: Kẻ thù luôn có âm mưu phá hoại cam kết. Ngay trước và sau Hiệp định, chính quyền Sài Gòn đã liên tiếp vi phạm bằng các chiến dịch "tràn ngập lãnh thổ". Bài học rút ra là phải luôn tôn trọng cam kết nhưng tuyệt đối không mơ hồ, luôn sẵn sàng lực lượng đối phó với mọi thủ đoạn tráo trở.
  - Xây dựng đội ngũ cán bộ ngoại giao: Sự thành công có được nhờ sự lãnh đạo sáng suốt của Đảng, đồng thời chọn lựa, rèn luyện được một đội ngũ cán bộ đối ngoại bản lĩnh, trí tuệ, xuất sắc trên bàn đàm phán.</t>
+  </si>
+  <si>
+    <t>CHAM_NGOI_CHO</t>
   </si>
 </sst>
 </file>
@@ -3049,7 +3034,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3092,9 +3077,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3463,7 +3445,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>11</v>
@@ -5504,19 +5486,19 @@
         <v>496</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>461</v>
@@ -6360,16 +6342,16 @@
         <v>138</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="179.4">
@@ -6906,14 +6888,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E485"/>
+  <dimension ref="A1:E401"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17" style="12" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="17.88671875" style="12" customWidth="1"/>
-    <col min="5" max="5" width="30.21875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="14" style="12" customWidth="1"/>
+    <col min="5" max="5" width="32" style="12" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
@@ -7037,7 +7019,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -7061,13 +7043,13 @@
         <v>158</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7078,7 +7060,7 @@
         <v>158</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>159</v>
@@ -7095,7 +7077,7 @@
         <v>158</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>159</v>
@@ -7112,13 +7094,13 @@
         <v>158</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>102</v>
+        <v>347</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>160</v>
+        <v>475</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7129,13 +7111,13 @@
         <v>158</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>347</v>
+        <v>452</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>475</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7146,7 +7128,7 @@
         <v>158</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>159</v>
@@ -7163,7 +7145,7 @@
         <v>158</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>159</v>
@@ -7180,7 +7162,7 @@
         <v>158</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>454</v>
+        <v>785</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>159</v>
@@ -7189,21 +7171,21 @@
         <v>160</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999" customHeight="1">
+    <row r="17" spans="1:5">
       <c r="A17" s="12" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>785</v>
+        <v>96</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7214,7 +7196,7 @@
         <v>158</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>159</v>
@@ -7231,7 +7213,7 @@
         <v>158</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>159</v>
@@ -7242,19 +7224,19 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="12" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7265,13 +7247,13 @@
         <v>158</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7282,24 +7264,24 @@
         <v>158</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="12" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>159</v>
@@ -7316,13 +7298,13 @@
         <v>158</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7333,30 +7315,30 @@
         <v>158</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>96</v>
+        <v>785</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.6" customHeight="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>785</v>
+        <v>109</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7367,18 +7349,18 @@
         <v>158</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="12" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>158</v>
@@ -7390,7 +7372,7 @@
         <v>159</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7401,7 +7383,7 @@
         <v>158</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>159</v>
@@ -7418,7 +7400,7 @@
         <v>158</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>159</v>
@@ -7429,19 +7411,19 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>160</v>
+        <v>530</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7452,13 +7434,13 @@
         <v>158</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7469,30 +7451,30 @@
         <v>158</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>160</v>
+        <v>530</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="12" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>162</v>
+        <v>530</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7503,7 +7485,7 @@
         <v>158</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D35" s="12" t="s">
         <v>159</v>
@@ -7520,13 +7502,13 @@
         <v>158</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>162</v>
+        <v>530</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7537,30 +7519,30 @@
         <v>158</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D37" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>160</v>
+        <v>530</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -7571,13 +7553,13 @@
         <v>158</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D39" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -7588,30 +7570,30 @@
         <v>158</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D40" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D41" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>162</v>
+        <v>530</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -7622,13 +7604,13 @@
         <v>158</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>162</v>
+        <v>530</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -7639,13 +7621,13 @@
         <v>158</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>160</v>
+        <v>530</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -7656,24 +7638,24 @@
         <v>158</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>160</v>
+        <v>530</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>159</v>
@@ -7690,7 +7672,7 @@
         <v>158</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D46" s="12" t="s">
         <v>159</v>
@@ -7701,19 +7683,19 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D47" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -7724,7 +7706,7 @@
         <v>158</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D48" s="12" t="s">
         <v>159</v>
@@ -7741,7 +7723,7 @@
         <v>158</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>159</v>
@@ -7752,19 +7734,19 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -7775,7 +7757,7 @@
         <v>158</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>159</v>
@@ -7792,7 +7774,7 @@
         <v>158</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>159</v>
@@ -7803,13 +7785,13 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D53" s="12" t="s">
         <v>159</v>
@@ -7826,41 +7808,41 @@
         <v>158</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="12" t="s">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>100</v>
+        <v>326</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>161</v>
+        <v>235</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="12" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>326</v>
+        <v>619</v>
       </c>
       <c r="D56" s="12" t="s">
         <v>159</v>
@@ -7871,30 +7853,30 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="12" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>619</v>
+        <v>333</v>
       </c>
       <c r="D57" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>235</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="12" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>333</v>
+        <v>628</v>
       </c>
       <c r="D58" s="12" t="s">
         <v>159</v>
@@ -7905,13 +7887,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="12" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>628</v>
+        <v>339</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>159</v>
@@ -7922,58 +7904,58 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="12" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>339</v>
+        <v>636</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="12" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>636</v>
+        <v>350</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>235</v>
+        <v>538</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="12" t="s">
-        <v>305</v>
+        <v>418</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>350</v>
+        <v>454</v>
       </c>
       <c r="D62" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>538</v>
+        <v>475</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>158</v>
@@ -7990,7 +7972,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>158</v>
@@ -8007,7 +7989,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>158</v>
@@ -8019,12 +8001,12 @@
         <v>159</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>475</v>
+        <v>530</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>158</v>
@@ -8036,69 +8018,69 @@
         <v>159</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>454</v>
+        <v>347</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="12" t="s">
-        <v>423</v>
+        <v>560</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>347</v>
+        <v>579</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="12" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D69" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="12" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D70" s="12" t="s">
         <v>159</v>
@@ -8109,19 +8091,19 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="12" t="s">
-        <v>574</v>
+        <v>10</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>587</v>
+        <v>119</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -8132,24 +8114,24 @@
         <v>158</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D72" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="12" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D73" s="12" t="s">
         <v>163</v>
@@ -8160,24 +8142,24 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="12" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D74" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="12" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>158</v>
@@ -8194,30 +8176,30 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="12" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D76" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="12" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D77" s="12" t="s">
         <v>163</v>
@@ -8228,30 +8210,30 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="12" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D78" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="12" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D79" s="12" t="s">
         <v>163</v>
@@ -8262,115 +8244,115 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="12" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D80" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="12" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>119</v>
+        <v>395</v>
       </c>
       <c r="D81" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>164</v>
+        <v>417</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="12" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="12" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>119</v>
+        <v>397</v>
       </c>
       <c r="D83" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>164</v>
+        <v>417</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="12" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D84" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="12" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D85" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="12" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>163</v>
@@ -8381,30 +8363,30 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="12" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D87" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="12" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>163</v>
@@ -8415,47 +8397,47 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="12" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D89" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="12" t="s">
-        <v>54</v>
+        <v>250</v>
       </c>
       <c r="B90" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>129</v>
+        <v>382</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>164</v>
+        <v>417</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="12" t="s">
-        <v>54</v>
+        <v>275</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>129</v>
+        <v>406</v>
       </c>
       <c r="D91" s="12" t="s">
         <v>163</v>
@@ -8466,30 +8448,30 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="12" t="s">
-        <v>54</v>
+        <v>286</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>125</v>
+        <v>409</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="12" t="s">
-        <v>54</v>
+        <v>297</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>163</v>
@@ -8500,30 +8482,30 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="12" t="s">
-        <v>62</v>
+        <v>305</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D94" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="12" t="s">
-        <v>62</v>
+        <v>421</v>
       </c>
       <c r="B95" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>129</v>
+        <v>470</v>
       </c>
       <c r="D95" s="12" t="s">
         <v>163</v>
@@ -8534,13 +8516,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="12" t="s">
-        <v>62</v>
+        <v>422</v>
       </c>
       <c r="B96" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>125</v>
+        <v>470</v>
       </c>
       <c r="D96" s="12" t="s">
         <v>163</v>
@@ -8551,30 +8533,30 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="12" t="s">
-        <v>62</v>
+        <v>560</v>
       </c>
       <c r="B97" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>397</v>
+        <v>123</v>
       </c>
       <c r="D97" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>417</v>
+        <v>164</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="12" t="s">
-        <v>65</v>
+        <v>574</v>
       </c>
       <c r="B98" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D98" s="12" t="s">
         <v>163</v>
@@ -8585,240 +8567,240 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="12" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="B99" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="12" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B100" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="12" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="B101" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="12" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="B102" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="12" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="B103" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="12" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B104" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="12" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="B105" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>411</v>
+        <v>141</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E105" s="12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="12" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B106" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B107" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E107" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="12" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>400</v>
+        <v>144</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E108" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="12" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B109" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B110" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="12" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>400</v>
+        <v>146</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B112" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E112" s="12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -8829,13 +8811,13 @@
         <v>158</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -8846,177 +8828,177 @@
         <v>158</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="12" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B115" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="12" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="B116" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="12" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="B117" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>403</v>
+        <v>370</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>417</v>
+        <v>171</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="12" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="B118" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>119</v>
+        <v>370</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="12" t="s">
-        <v>421</v>
+        <v>297</v>
       </c>
       <c r="B119" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>470</v>
+        <v>370</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E119" s="12" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="12" t="s">
-        <v>422</v>
+        <v>305</v>
       </c>
       <c r="B120" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>470</v>
+        <v>141</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="12" t="s">
-        <v>560</v>
+        <v>418</v>
       </c>
       <c r="B121" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E121" s="12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="12" t="s">
-        <v>560</v>
+        <v>419</v>
       </c>
       <c r="B122" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="12" t="s">
-        <v>574</v>
+        <v>420</v>
       </c>
       <c r="B123" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E123" s="12" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="12" t="s">
-        <v>10</v>
+        <v>421</v>
       </c>
       <c r="B124" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D124" s="12" t="s">
         <v>166</v>
@@ -9027,41 +9009,41 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="12" t="s">
-        <v>10</v>
+        <v>422</v>
       </c>
       <c r="B125" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D125" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="12" t="s">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="B126" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>141</v>
+        <v>473</v>
       </c>
       <c r="D126" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E126" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="12" t="s">
-        <v>27</v>
+        <v>560</v>
       </c>
       <c r="B127" s="12" t="s">
         <v>158</v>
@@ -9078,7 +9060,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="12" t="s">
-        <v>34</v>
+        <v>567</v>
       </c>
       <c r="B128" s="12" t="s">
         <v>158</v>
@@ -9095,7 +9077,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="12" t="s">
-        <v>34</v>
+        <v>574</v>
       </c>
       <c r="B129" s="12" t="s">
         <v>158</v>
@@ -9107,15 +9089,15 @@
         <v>166</v>
       </c>
       <c r="E129" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="12" t="s">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C130" s="12" t="s">
         <v>141</v>
@@ -9124,32 +9106,32 @@
         <v>166</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="12" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D131" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>171</v>
+        <v>230</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="12" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C132" s="12" t="s">
         <v>141</v>
@@ -9158,15 +9140,15 @@
         <v>166</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="12" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C133" s="12" t="s">
         <v>144</v>
@@ -9175,66 +9157,66 @@
         <v>166</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="12" t="s">
-        <v>54</v>
+        <v>123</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D134" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="12" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D135" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E135" s="12" t="s">
-        <v>171</v>
+        <v>230</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="12" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D136" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E136" s="12" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="12" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C137" s="12" t="s">
         <v>144</v>
@@ -9243,49 +9225,49 @@
         <v>166</v>
       </c>
       <c r="E137" s="12" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="12" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D138" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E138" s="12" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="12" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D139" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="12" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>144</v>
@@ -9294,66 +9276,66 @@
         <v>166</v>
       </c>
       <c r="E140" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="12" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D141" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E141" s="12" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="12" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D142" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E142" s="12" t="s">
-        <v>171</v>
+        <v>230</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="12" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D143" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E143" s="12" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="12" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>146</v>
@@ -9362,15 +9344,15 @@
         <v>166</v>
       </c>
       <c r="E144" s="12" t="s">
-        <v>171</v>
+        <v>230</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="12" t="s">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C145" s="12" t="s">
         <v>141</v>
@@ -9379,500 +9361,500 @@
         <v>166</v>
       </c>
       <c r="E145" s="12" t="s">
-        <v>171</v>
+        <v>230</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="12" t="s">
-        <v>250</v>
+        <v>470</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>369</v>
+        <v>150</v>
       </c>
       <c r="D146" s="12" t="s">
         <v>166</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="12" t="s">
-        <v>260</v>
+        <v>119</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>413</v>
+        <v>92</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E147" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="12" t="s">
-        <v>268</v>
+        <v>119</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>415</v>
+        <v>96</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="12" t="s">
-        <v>275</v>
+        <v>119</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>370</v>
+        <v>100</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="12" t="s">
-        <v>286</v>
+        <v>119</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="12" t="s">
-        <v>297</v>
+        <v>119</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E151" s="12" t="s">
-        <v>171</v>
+        <v>539</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="12" t="s">
-        <v>305</v>
+        <v>119</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>141</v>
+        <v>451</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="12" t="s">
-        <v>418</v>
+        <v>123</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="12" t="s">
-        <v>419</v>
+        <v>123</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>171</v>
+        <v>532</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="12" t="s">
-        <v>420</v>
+        <v>123</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>171</v>
+        <v>532</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="12" t="s">
-        <v>421</v>
+        <v>123</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E156" s="12" t="s">
-        <v>171</v>
+        <v>532</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="12" t="s">
-        <v>422</v>
+        <v>123</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>171</v>
+        <v>532</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="12" t="s">
-        <v>423</v>
+        <v>123</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>473</v>
+        <v>107</v>
       </c>
       <c r="D158" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>172</v>
+        <v>532</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="12" t="s">
-        <v>560</v>
+        <v>123</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>141</v>
+        <v>452</v>
       </c>
       <c r="D159" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>171</v>
+        <v>532</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="12" t="s">
-        <v>567</v>
+        <v>123</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>141</v>
+        <v>453</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>171</v>
+        <v>532</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="12" t="s">
-        <v>574</v>
+        <v>123</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>141</v>
+        <v>454</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E161" s="12" t="s">
-        <v>171</v>
+        <v>532</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="12" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B162" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E162" s="12" t="s">
-        <v>165</v>
+        <v>532</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="12" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B163" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>230</v>
+        <v>532</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B164" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E164" s="12" t="s">
-        <v>231</v>
+        <v>168</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B165" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>167</v>
+        <v>532</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B166" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>231</v>
+        <v>168</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="12" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B167" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>230</v>
+        <v>533</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="12" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B168" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="D168" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E168" s="12" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B169" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>231</v>
+        <v>533</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B170" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C170" s="12" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B171" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E171" s="12" t="s">
-        <v>231</v>
+        <v>168</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B172" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E172" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B173" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>146</v>
+        <v>109</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E173" s="12" t="s">
-        <v>231</v>
+        <v>168</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B174" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E174" s="12" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -9883,132 +9865,132 @@
         <v>163</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="D175" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E175" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="12" t="s">
-        <v>129</v>
+        <v>382</v>
       </c>
       <c r="B176" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>146</v>
+        <v>326</v>
       </c>
       <c r="D176" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>230</v>
+        <v>480</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="12" t="s">
-        <v>464</v>
+        <v>383</v>
       </c>
       <c r="B177" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>141</v>
+        <v>339</v>
       </c>
       <c r="D177" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E177" s="12" t="s">
-        <v>230</v>
+        <v>532</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="12" t="s">
-        <v>470</v>
+        <v>409</v>
       </c>
       <c r="B178" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>150</v>
+        <v>339</v>
       </c>
       <c r="D178" s="12" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E178" s="12" t="s">
-        <v>231</v>
+        <v>161</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="12" t="s">
-        <v>119</v>
+        <v>464</v>
       </c>
       <c r="B179" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>92</v>
+        <v>347</v>
       </c>
       <c r="D179" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E179" s="12" t="s">
-        <v>168</v>
+        <v>532</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="12" t="s">
-        <v>119</v>
+        <v>470</v>
       </c>
       <c r="B180" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>96</v>
+        <v>452</v>
       </c>
       <c r="D180" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E180" s="12" t="s">
-        <v>168</v>
+        <v>533</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="12" t="s">
-        <v>119</v>
+        <v>470</v>
       </c>
       <c r="B181" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>100</v>
+        <v>453</v>
       </c>
       <c r="D181" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E181" s="12" t="s">
-        <v>168</v>
+        <v>533</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="12" t="s">
-        <v>119</v>
+        <v>470</v>
       </c>
       <c r="B182" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>347</v>
+        <v>454</v>
       </c>
       <c r="D182" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E182" s="12" t="s">
-        <v>161</v>
+        <v>533</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -10019,13 +10001,13 @@
         <v>163</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>350</v>
+        <v>135</v>
       </c>
       <c r="D183" s="12" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E183" s="12" t="s">
-        <v>539</v>
+        <v>170</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -10036,115 +10018,115 @@
         <v>163</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>451</v>
+        <v>137</v>
       </c>
       <c r="D184" s="12" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E184" s="12" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="12" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B185" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="D185" s="12" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E185" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="12" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B186" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="D186" s="12" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E186" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="12" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B187" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="D187" s="12" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E187" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>103</v>
+        <v>248</v>
       </c>
       <c r="D188" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E188" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="12" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B189" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="D189" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E189" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B190" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>107</v>
+        <v>248</v>
       </c>
       <c r="D190" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E190" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -10155,13 +10137,13 @@
         <v>163</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>452</v>
+        <v>246</v>
       </c>
       <c r="D191" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E191" s="12" t="s">
-        <v>532</v>
+        <v>364</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -10172,13 +10154,13 @@
         <v>163</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>453</v>
+        <v>247</v>
       </c>
       <c r="D192" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E192" s="12" t="s">
-        <v>532</v>
+        <v>364</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -10189,30 +10171,30 @@
         <v>163</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>454</v>
+        <v>248</v>
       </c>
       <c r="D193" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E193" s="12" t="s">
-        <v>532</v>
+        <v>364</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>96</v>
+        <v>249</v>
       </c>
       <c r="D194" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E194" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -10223,228 +10205,228 @@
         <v>163</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>100</v>
+        <v>248</v>
       </c>
       <c r="D195" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E195" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B196" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>103</v>
+        <v>248</v>
       </c>
       <c r="D196" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E196" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B197" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>105</v>
+        <v>247</v>
       </c>
       <c r="D197" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E197" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>107</v>
+        <v>248</v>
       </c>
       <c r="D198" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E198" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B199" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="D199" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E199" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="12" t="s">
-        <v>128</v>
+        <v>381</v>
       </c>
       <c r="B200" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>98</v>
+        <v>243</v>
       </c>
       <c r="D200" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E200" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="12" t="s">
-        <v>128</v>
+        <v>382</v>
       </c>
       <c r="B201" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>102</v>
+        <v>243</v>
       </c>
       <c r="D201" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E201" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="12" t="s">
-        <v>128</v>
+        <v>383</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="D202" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E202" s="12" t="s">
-        <v>168</v>
+        <v>364</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="12" t="s">
-        <v>129</v>
+        <v>467</v>
       </c>
       <c r="B203" s="12" t="s">
         <v>163</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="D203" s="12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E203" s="12" t="s">
-        <v>168</v>
+        <v>476</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="12" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B204" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>100</v>
+        <v>451</v>
       </c>
       <c r="D204" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E204" s="12" t="s">
-        <v>168</v>
+        <v>534</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="12" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B205" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>109</v>
+        <v>452</v>
       </c>
       <c r="D205" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E205" s="12" t="s">
-        <v>168</v>
+        <v>534</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="12" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B206" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>111</v>
+        <v>453</v>
       </c>
       <c r="D206" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E206" s="12" t="s">
-        <v>168</v>
+        <v>535</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="12" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B207" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>112</v>
+        <v>454</v>
       </c>
       <c r="D207" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E207" s="12" t="s">
-        <v>168</v>
+        <v>536</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="12" t="s">
-        <v>382</v>
+        <v>141</v>
       </c>
       <c r="B208" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="D208" s="12" t="s">
         <v>159</v>
@@ -10455,282 +10437,282 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="12" t="s">
-        <v>383</v>
+        <v>146</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>339</v>
+        <v>94</v>
       </c>
       <c r="D209" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E209" s="12" t="s">
-        <v>532</v>
+        <v>235</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="12" t="s">
-        <v>409</v>
+        <v>146</v>
       </c>
       <c r="B210" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>339</v>
+        <v>102</v>
       </c>
       <c r="D210" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E210" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="12" t="s">
-        <v>464</v>
+        <v>146</v>
       </c>
       <c r="B211" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>347</v>
+        <v>105</v>
       </c>
       <c r="D211" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E211" s="12" t="s">
-        <v>532</v>
+        <v>162</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="12" t="s">
-        <v>470</v>
+        <v>150</v>
       </c>
       <c r="B212" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>452</v>
+        <v>92</v>
       </c>
       <c r="D212" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E212" s="12" t="s">
-        <v>533</v>
+        <v>162</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="12" t="s">
-        <v>470</v>
+        <v>150</v>
       </c>
       <c r="B213" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D213" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E213" s="12" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="12" t="s">
-        <v>470</v>
+        <v>150</v>
       </c>
       <c r="B214" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D214" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E214" s="12" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="12" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="B215" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>135</v>
+        <v>454</v>
       </c>
       <c r="D215" s="12" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E215" s="12" t="s">
-        <v>170</v>
+        <v>537</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="12" t="s">
-        <v>123</v>
+        <v>369</v>
       </c>
       <c r="B216" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>135</v>
+        <v>326</v>
       </c>
       <c r="D216" s="12" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E216" s="12" t="s">
-        <v>170</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="12" t="s">
-        <v>119</v>
+        <v>370</v>
       </c>
       <c r="B217" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>137</v>
+        <v>339</v>
       </c>
       <c r="D217" s="12" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E217" s="12" t="s">
-        <v>170</v>
+        <v>534</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="12" t="s">
-        <v>127</v>
+        <v>374</v>
       </c>
       <c r="B218" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>137</v>
+        <v>339</v>
       </c>
       <c r="D218" s="12" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E218" s="12" t="s">
-        <v>170</v>
+        <v>537</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="12" t="s">
-        <v>128</v>
+        <v>415</v>
       </c>
       <c r="B219" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="D219" s="12" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E219" s="12" t="s">
-        <v>170</v>
+        <v>534</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="12" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B220" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D220" s="12" t="s">
         <v>169</v>
       </c>
       <c r="E220" s="12" t="s">
-        <v>170</v>
+        <v>233</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="12" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B221" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="D221" s="12" t="s">
-        <v>365</v>
+        <v>169</v>
       </c>
       <c r="E221" s="12" t="s">
-        <v>364</v>
+        <v>233</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="12" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="B222" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>249</v>
+        <v>137</v>
       </c>
       <c r="D222" s="12" t="s">
-        <v>365</v>
+        <v>169</v>
       </c>
       <c r="E222" s="12" t="s">
-        <v>364</v>
+        <v>233</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="12" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="B223" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="D223" s="12" t="s">
-        <v>365</v>
+        <v>169</v>
       </c>
       <c r="E223" s="12" t="s">
-        <v>364</v>
+        <v>233</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="12" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B224" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>246</v>
+        <v>135</v>
       </c>
       <c r="D224" s="12" t="s">
-        <v>365</v>
+        <v>169</v>
       </c>
       <c r="E224" s="12" t="s">
-        <v>364</v>
+        <v>233</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="12" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B225" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C225" s="12" t="s">
         <v>247</v>
@@ -10744,10 +10726,10 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="12" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B226" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C226" s="12" t="s">
         <v>248</v>
@@ -10761,13 +10743,13 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="12" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="B227" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C227" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D227" s="12" t="s">
         <v>365</v>
@@ -10778,10 +10760,10 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="12" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="B228" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C228" s="12" t="s">
         <v>248</v>
@@ -10795,13 +10777,13 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="12" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B229" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C229" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D229" s="12" t="s">
         <v>365</v>
@@ -10812,10 +10794,10 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="12" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="B230" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C230" s="12" t="s">
         <v>247</v>
@@ -10829,13 +10811,13 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="12" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="B231" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C231" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D231" s="12" t="s">
         <v>365</v>
@@ -10846,10 +10828,10 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="12" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="B232" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C232" s="12" t="s">
         <v>248</v>
@@ -10863,13 +10845,13 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="12" t="s">
-        <v>381</v>
+        <v>152</v>
       </c>
       <c r="B233" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C233" s="12" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D233" s="12" t="s">
         <v>365</v>
@@ -10880,13 +10862,13 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="12" t="s">
-        <v>382</v>
+        <v>152</v>
       </c>
       <c r="B234" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C234" s="12" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D234" s="12" t="s">
         <v>365</v>
@@ -10897,13 +10879,13 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="12" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="B235" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C235" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D235" s="12" t="s">
         <v>365</v>
@@ -10914,163 +10896,163 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="12" t="s">
-        <v>467</v>
+        <v>369</v>
       </c>
       <c r="B236" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C236" s="12" t="s">
-        <v>123</v>
+        <v>243</v>
       </c>
       <c r="D236" s="12" t="s">
-        <v>163</v>
+        <v>365</v>
       </c>
       <c r="E236" s="12" t="s">
-        <v>476</v>
+        <v>364</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="12" t="s">
-        <v>141</v>
+        <v>370</v>
       </c>
       <c r="B237" s="12" t="s">
         <v>166</v>
       </c>
       <c r="C237" s="12" t="s">
-        <v>451</v>
+        <v>245</v>
       </c>
       <c r="D237" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E237" s="12" t="s">
-        <v>534</v>
+        <v>364</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="12" t="s">
-        <v>141</v>
+        <v>372</v>
       </c>
       <c r="B238" s="12" t="s">
         <v>166</v>
       </c>
       <c r="C238" s="12" t="s">
-        <v>452</v>
+        <v>244</v>
       </c>
       <c r="D238" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E238" s="12" t="s">
-        <v>534</v>
+        <v>364</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="12" t="s">
-        <v>141</v>
+        <v>373</v>
       </c>
       <c r="B239" s="12" t="s">
         <v>166</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>453</v>
+        <v>245</v>
       </c>
       <c r="D239" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E239" s="12" t="s">
-        <v>535</v>
+        <v>364</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="12" t="s">
-        <v>141</v>
+        <v>374</v>
       </c>
       <c r="B240" s="12" t="s">
         <v>166</v>
       </c>
       <c r="C240" s="12" t="s">
-        <v>454</v>
+        <v>245</v>
       </c>
       <c r="D240" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E240" s="12" t="s">
-        <v>536</v>
+        <v>364</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="12" t="s">
-        <v>141</v>
+        <v>473</v>
       </c>
       <c r="B241" s="12" t="s">
         <v>166</v>
       </c>
       <c r="C241" s="12" t="s">
-        <v>347</v>
+        <v>150</v>
       </c>
       <c r="D241" s="12" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E241" s="12" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="12" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="B242" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="D242" s="12" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E242" s="12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="12" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="B243" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C243" s="12" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="D243" s="12" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E243" s="12" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="12" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="B244" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C244" s="12" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="D244" s="12" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E244" s="12" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="12" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B245" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C245" s="12" t="s">
         <v>92</v>
@@ -11079,222 +11061,222 @@
         <v>159</v>
       </c>
       <c r="E245" s="12" t="s">
-        <v>162</v>
+        <v>234</v>
       </c>
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="12" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B246" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C246" s="12" t="s">
-        <v>452</v>
+        <v>98</v>
       </c>
       <c r="D246" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E246" s="12" t="s">
-        <v>537</v>
+        <v>234</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="12" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B247" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C247" s="12" t="s">
-        <v>453</v>
+        <v>247</v>
       </c>
       <c r="D247" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E247" s="12" t="s">
-        <v>537</v>
+        <v>364</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="12" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B248" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C248" s="12" t="s">
-        <v>454</v>
+        <v>248</v>
       </c>
       <c r="D248" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E248" s="12" t="s">
-        <v>537</v>
+        <v>364</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="12" t="s">
-        <v>369</v>
+        <v>137</v>
       </c>
       <c r="B249" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C249" s="12" t="s">
-        <v>326</v>
+        <v>248</v>
       </c>
       <c r="D249" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E249" s="12" t="s">
-        <v>479</v>
+        <v>364</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="12" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B250" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C250" s="12" t="s">
-        <v>339</v>
+        <v>247</v>
       </c>
       <c r="D250" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E250" s="12" t="s">
-        <v>534</v>
+        <v>364</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="12" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B251" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C251" s="12" t="s">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="D251" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E251" s="12" t="s">
-        <v>537</v>
+        <v>364</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="12" t="s">
-        <v>415</v>
+        <v>10</v>
       </c>
       <c r="B252" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C252" s="12" t="s">
-        <v>333</v>
+        <v>246</v>
       </c>
       <c r="D252" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E252" s="12" t="s">
-        <v>534</v>
+        <v>364</v>
       </c>
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="12" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="B253" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C253" s="12" t="s">
-        <v>135</v>
+        <v>247</v>
       </c>
       <c r="D253" s="12" t="s">
-        <v>169</v>
+        <v>365</v>
       </c>
       <c r="E253" s="12" t="s">
-        <v>233</v>
+        <v>364</v>
       </c>
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="12" t="s">
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="B254" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C254" s="12" t="s">
-        <v>137</v>
+        <v>248</v>
       </c>
       <c r="D254" s="12" t="s">
-        <v>169</v>
+        <v>365</v>
       </c>
       <c r="E254" s="12" t="s">
-        <v>233</v>
+        <v>364</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="12" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="B255" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C255" s="12" t="s">
-        <v>137</v>
+        <v>246</v>
       </c>
       <c r="D255" s="12" t="s">
-        <v>169</v>
+        <v>365</v>
       </c>
       <c r="E255" s="12" t="s">
-        <v>233</v>
+        <v>364</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="12" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="B256" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C256" s="12" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="D256" s="12" t="s">
-        <v>169</v>
+        <v>365</v>
       </c>
       <c r="E256" s="12" t="s">
-        <v>233</v>
+        <v>364</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="12" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="B257" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C257" s="12" t="s">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="D257" s="12" t="s">
-        <v>169</v>
+        <v>365</v>
       </c>
       <c r="E257" s="12" t="s">
-        <v>233</v>
+        <v>364</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="12" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="B258" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D258" s="12" t="s">
         <v>365</v>
@@ -11305,13 +11287,13 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="12" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="B259" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C259" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D259" s="12" t="s">
         <v>365</v>
@@ -11322,13 +11304,13 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="12" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="B260" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C260" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D260" s="12" t="s">
         <v>365</v>
@@ -11339,10 +11321,10 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="12" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="B261" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C261" s="12" t="s">
         <v>248</v>
@@ -11356,13 +11338,13 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="12" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="B262" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C262" s="12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D262" s="12" t="s">
         <v>365</v>
@@ -11373,13 +11355,13 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="12" t="s">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="B263" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C263" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D263" s="12" t="s">
         <v>365</v>
@@ -11390,10 +11372,10 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="12" t="s">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="B264" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C264" s="12" t="s">
         <v>247</v>
@@ -11407,10 +11389,10 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="12" t="s">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="B265" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C265" s="12" t="s">
         <v>248</v>
@@ -11424,13 +11406,13 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="12" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="B266" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D266" s="12" t="s">
         <v>365</v>
@@ -11441,13 +11423,13 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="12" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
       <c r="B267" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C267" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D267" s="12" t="s">
         <v>365</v>
@@ -11458,13 +11440,13 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="12" t="s">
-        <v>366</v>
+        <v>40</v>
       </c>
       <c r="B268" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D268" s="12" t="s">
         <v>365</v>
@@ -11475,13 +11457,13 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="12" t="s">
-        <v>369</v>
+        <v>40</v>
       </c>
       <c r="B269" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D269" s="12" t="s">
         <v>365</v>
@@ -11492,13 +11474,13 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="12" t="s">
-        <v>370</v>
+        <v>40</v>
       </c>
       <c r="B270" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C270" s="12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D270" s="12" t="s">
         <v>365</v>
@@ -11509,13 +11491,13 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="12" t="s">
-        <v>372</v>
+        <v>46</v>
       </c>
       <c r="B271" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C271" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D271" s="12" t="s">
         <v>365</v>
@@ -11526,13 +11508,13 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="12" t="s">
-        <v>373</v>
+        <v>46</v>
       </c>
       <c r="B272" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C272" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D272" s="12" t="s">
         <v>365</v>
@@ -11543,13 +11525,13 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="12" t="s">
-        <v>374</v>
+        <v>46</v>
       </c>
       <c r="B273" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C273" s="12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D273" s="12" t="s">
         <v>365</v>
@@ -11560,132 +11542,132 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="12" t="s">
-        <v>473</v>
+        <v>50</v>
       </c>
       <c r="B274" s="12" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C274" s="12" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="D274" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E274" s="12" t="s">
-        <v>477</v>
+        <v>364</v>
       </c>
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="12" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B275" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C275" s="12" t="s">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="D275" s="12" t="s">
-        <v>169</v>
+        <v>365</v>
       </c>
       <c r="E275" s="12" t="s">
-        <v>232</v>
+        <v>364</v>
       </c>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="12" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B276" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C276" s="12" t="s">
-        <v>137</v>
+        <v>249</v>
       </c>
       <c r="D276" s="12" t="s">
-        <v>169</v>
+        <v>365</v>
       </c>
       <c r="E276" s="12" t="s">
-        <v>232</v>
+        <v>364</v>
       </c>
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="12" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="B277" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C277" s="12" t="s">
-        <v>137</v>
+        <v>246</v>
       </c>
       <c r="D277" s="12" t="s">
-        <v>169</v>
+        <v>365</v>
       </c>
       <c r="E277" s="12" t="s">
-        <v>232</v>
+        <v>364</v>
       </c>
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="12" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="B278" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C278" s="12" t="s">
-        <v>137</v>
+        <v>247</v>
       </c>
       <c r="D278" s="12" t="s">
-        <v>169</v>
+        <v>365</v>
       </c>
       <c r="E278" s="12" t="s">
-        <v>232</v>
+        <v>364</v>
       </c>
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="12" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="B279" s="12" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C279" s="12" t="s">
-        <v>92</v>
+        <v>248</v>
       </c>
       <c r="D279" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E279" s="12" t="s">
-        <v>234</v>
+        <v>364</v>
       </c>
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="12" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="B280" s="12" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C280" s="12" t="s">
-        <v>98</v>
+        <v>247</v>
       </c>
       <c r="D280" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E280" s="12" t="s">
-        <v>234</v>
+        <v>364</v>
       </c>
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="12" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="B281" s="12" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C281" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D281" s="12" t="s">
         <v>365</v>
@@ -11696,13 +11678,13 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="12" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="B282" s="12" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C282" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D282" s="12" t="s">
         <v>365</v>
@@ -11713,10 +11695,10 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="12" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="B283" s="12" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C283" s="12" t="s">
         <v>248</v>
@@ -11730,10 +11712,10 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="12" t="s">
-        <v>375</v>
+        <v>67</v>
       </c>
       <c r="B284" s="12" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C284" s="12" t="s">
         <v>247</v>
@@ -11747,13 +11729,13 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="12" t="s">
-        <v>377</v>
+        <v>67</v>
       </c>
       <c r="B285" s="12" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C285" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D285" s="12" t="s">
         <v>365</v>
@@ -11764,336 +11746,336 @@
     </row>
     <row r="286" spans="1:5">
       <c r="A286" s="12" t="s">
-        <v>574</v>
+        <v>71</v>
       </c>
       <c r="B286" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C286" s="12" t="s">
-        <v>121</v>
+        <v>246</v>
       </c>
       <c r="D286" s="12" t="s">
-        <v>163</v>
+        <v>365</v>
       </c>
       <c r="E286" s="12" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
     </row>
     <row r="287" spans="1:5">
       <c r="A287" s="12" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="B287" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>141</v>
+        <v>247</v>
       </c>
       <c r="D287" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E287" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="12" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B288" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C288" s="12" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="D288" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E288" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="289" spans="1:5">
       <c r="A289" s="12" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B289" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C289" s="12" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="D289" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E289" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="290" spans="1:5">
       <c r="A290" s="12" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B290" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>144</v>
+        <v>248</v>
       </c>
       <c r="D290" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E290" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="291" spans="1:5">
       <c r="A291" s="12" t="s">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="B291" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>370</v>
+        <v>247</v>
       </c>
       <c r="D291" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E291" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="292" spans="1:5">
       <c r="A292" s="12" t="s">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="B292" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="D292" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E292" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="293" spans="1:5">
       <c r="A293" s="12" t="s">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="B293" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>141</v>
+        <v>249</v>
       </c>
       <c r="D293" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E293" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="294" spans="1:5">
       <c r="A294" s="12" t="s">
-        <v>419</v>
+        <v>250</v>
       </c>
       <c r="B294" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="D294" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E294" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="295" spans="1:5">
       <c r="A295" s="12" t="s">
-        <v>420</v>
+        <v>260</v>
       </c>
       <c r="B295" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>141</v>
+        <v>244</v>
       </c>
       <c r="D295" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E295" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="296" spans="1:5">
       <c r="A296" s="12" t="s">
-        <v>421</v>
+        <v>268</v>
       </c>
       <c r="B296" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="D296" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E296" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="297" spans="1:5">
       <c r="A297" s="12" t="s">
-        <v>422</v>
+        <v>268</v>
       </c>
       <c r="B297" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>150</v>
+        <v>245</v>
       </c>
       <c r="D297" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E297" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="298" spans="1:5">
       <c r="A298" s="12" t="s">
-        <v>560</v>
+        <v>275</v>
       </c>
       <c r="B298" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="D298" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E298" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="299" spans="1:5">
       <c r="A299" s="12" t="s">
-        <v>567</v>
+        <v>286</v>
       </c>
       <c r="B299" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="D299" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E299" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="300" spans="1:5">
       <c r="A300" s="12" t="s">
-        <v>574</v>
+        <v>297</v>
       </c>
       <c r="B300" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>141</v>
+        <v>246</v>
       </c>
       <c r="D300" s="12" t="s">
-        <v>166</v>
+        <v>365</v>
       </c>
       <c r="E300" s="12" t="s">
-        <v>171</v>
+        <v>364</v>
       </c>
     </row>
     <row r="301" spans="1:5">
       <c r="A301" s="12" t="s">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="B301" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>619</v>
+        <v>246</v>
       </c>
       <c r="D301" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E301" s="12" t="s">
-        <v>235</v>
+        <v>364</v>
       </c>
     </row>
     <row r="302" spans="1:5">
       <c r="A302" s="12" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="B302" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>628</v>
+        <v>247</v>
       </c>
       <c r="D302" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E302" s="12" t="s">
-        <v>160</v>
+        <v>364</v>
       </c>
     </row>
     <row r="303" spans="1:5">
       <c r="A303" s="12" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B303" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>636</v>
+        <v>248</v>
       </c>
       <c r="D303" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E303" s="12" t="s">
-        <v>235</v>
+        <v>364</v>
       </c>
     </row>
     <row r="304" spans="1:5">
       <c r="A304" s="12" t="s">
-        <v>423</v>
+        <v>305</v>
       </c>
       <c r="B304" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C304" s="12" t="s">
-        <v>347</v>
+        <v>249</v>
       </c>
       <c r="D304" s="12" t="s">
-        <v>159</v>
+        <v>365</v>
       </c>
       <c r="E304" s="12" t="s">
-        <v>162</v>
+        <v>364</v>
       </c>
     </row>
     <row r="305" spans="1:5">
       <c r="A305" s="12" t="s">
-        <v>10</v>
+        <v>418</v>
       </c>
       <c r="B305" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C305" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D305" s="12" t="s">
         <v>365</v>
@@ -12104,7 +12086,7 @@
     </row>
     <row r="306" spans="1:5">
       <c r="A306" s="12" t="s">
-        <v>10</v>
+        <v>419</v>
       </c>
       <c r="B306" s="12" t="s">
         <v>158</v>
@@ -12121,13 +12103,13 @@
     </row>
     <row r="307" spans="1:5">
       <c r="A307" s="12" t="s">
-        <v>10</v>
+        <v>420</v>
       </c>
       <c r="B307" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C307" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D307" s="12" t="s">
         <v>365</v>
@@ -12138,13 +12120,13 @@
     </row>
     <row r="308" spans="1:5">
       <c r="A308" s="12" t="s">
-        <v>20</v>
+        <v>421</v>
       </c>
       <c r="B308" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C308" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D308" s="12" t="s">
         <v>365</v>
@@ -12155,7 +12137,7 @@
     </row>
     <row r="309" spans="1:5">
       <c r="A309" s="12" t="s">
-        <v>20</v>
+        <v>422</v>
       </c>
       <c r="B309" s="12" t="s">
         <v>158</v>
@@ -12172,13 +12154,13 @@
     </row>
     <row r="310" spans="1:5">
       <c r="A310" s="12" t="s">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="B310" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C310" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D310" s="12" t="s">
         <v>365</v>
@@ -12189,13 +12171,13 @@
     </row>
     <row r="311" spans="1:5">
       <c r="A311" s="12" t="s">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="B311" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C311" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D311" s="12" t="s">
         <v>365</v>
@@ -12206,13 +12188,13 @@
     </row>
     <row r="312" spans="1:5">
       <c r="A312" s="12" t="s">
-        <v>27</v>
+        <v>560</v>
       </c>
       <c r="B312" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C312" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D312" s="12" t="s">
         <v>365</v>
@@ -12223,13 +12205,13 @@
     </row>
     <row r="313" spans="1:5">
       <c r="A313" s="12" t="s">
-        <v>27</v>
+        <v>560</v>
       </c>
       <c r="B313" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C313" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D313" s="12" t="s">
         <v>365</v>
@@ -12240,13 +12222,13 @@
     </row>
     <row r="314" spans="1:5">
       <c r="A314" s="12" t="s">
-        <v>27</v>
+        <v>560</v>
       </c>
       <c r="B314" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C314" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D314" s="12" t="s">
         <v>365</v>
@@ -12257,13 +12239,13 @@
     </row>
     <row r="315" spans="1:5">
       <c r="A315" s="12" t="s">
-        <v>27</v>
+        <v>567</v>
       </c>
       <c r="B315" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C315" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D315" s="12" t="s">
         <v>365</v>
@@ -12274,13 +12256,13 @@
     </row>
     <row r="316" spans="1:5">
       <c r="A316" s="12" t="s">
-        <v>34</v>
+        <v>574</v>
       </c>
       <c r="B316" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C316" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D316" s="12" t="s">
         <v>365</v>
@@ -12291,10 +12273,10 @@
     </row>
     <row r="317" spans="1:5">
       <c r="A317" s="12" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="B317" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C317" s="12" t="s">
         <v>247</v>
@@ -12308,10 +12290,10 @@
     </row>
     <row r="318" spans="1:5">
       <c r="A318" s="12" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="B318" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C318" s="12" t="s">
         <v>248</v>
@@ -12325,13 +12307,13 @@
     </row>
     <row r="319" spans="1:5">
       <c r="A319" s="12" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="B319" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C319" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D319" s="12" t="s">
         <v>365</v>
@@ -12342,13 +12324,13 @@
     </row>
     <row r="320" spans="1:5">
       <c r="A320" s="12" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="B320" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C320" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D320" s="12" t="s">
         <v>365</v>
@@ -12359,13 +12341,13 @@
     </row>
     <row r="321" spans="1:5">
       <c r="A321" s="12" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="B321" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C321" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D321" s="12" t="s">
         <v>365</v>
@@ -12376,10 +12358,10 @@
     </row>
     <row r="322" spans="1:5">
       <c r="A322" s="12" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="B322" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C322" s="12" t="s">
         <v>248</v>
@@ -12393,13 +12375,13 @@
     </row>
     <row r="323" spans="1:5">
       <c r="A323" s="12" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="B323" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C323" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D323" s="12" t="s">
         <v>365</v>
@@ -12410,13 +12392,13 @@
     </row>
     <row r="324" spans="1:5">
       <c r="A324" s="12" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="B324" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C324" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D324" s="12" t="s">
         <v>365</v>
@@ -12427,10 +12409,10 @@
     </row>
     <row r="325" spans="1:5">
       <c r="A325" s="12" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="B325" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C325" s="12" t="s">
         <v>248</v>
@@ -12444,13 +12426,13 @@
     </row>
     <row r="326" spans="1:5">
       <c r="A326" s="12" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="B326" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C326" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D326" s="12" t="s">
         <v>365</v>
@@ -12461,13 +12443,13 @@
     </row>
     <row r="327" spans="1:5">
       <c r="A327" s="12" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="B327" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C327" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D327" s="12" t="s">
         <v>365</v>
@@ -12478,10 +12460,10 @@
     </row>
     <row r="328" spans="1:5">
       <c r="A328" s="12" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="B328" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C328" s="12" t="s">
         <v>248</v>
@@ -12495,13 +12477,13 @@
     </row>
     <row r="329" spans="1:5">
       <c r="A329" s="12" t="s">
-        <v>50</v>
+        <v>326</v>
       </c>
       <c r="B329" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C329" s="12" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D329" s="12" t="s">
         <v>365</v>
@@ -12512,13 +12494,13 @@
     </row>
     <row r="330" spans="1:5">
       <c r="A330" s="12" t="s">
-        <v>54</v>
+        <v>333</v>
       </c>
       <c r="B330" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C330" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D330" s="12" t="s">
         <v>365</v>
@@ -12529,13 +12511,13 @@
     </row>
     <row r="331" spans="1:5">
       <c r="A331" s="12" t="s">
-        <v>54</v>
+        <v>339</v>
       </c>
       <c r="B331" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C331" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D331" s="12" t="s">
         <v>365</v>
@@ -12546,13 +12528,13 @@
     </row>
     <row r="332" spans="1:5">
       <c r="A332" s="12" t="s">
-        <v>54</v>
+        <v>347</v>
       </c>
       <c r="B332" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C332" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D332" s="12" t="s">
         <v>365</v>
@@ -12563,13 +12545,13 @@
     </row>
     <row r="333" spans="1:5">
       <c r="A333" s="12" t="s">
-        <v>62</v>
+        <v>350</v>
       </c>
       <c r="B333" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C333" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D333" s="12" t="s">
         <v>365</v>
@@ -12580,13 +12562,13 @@
     </row>
     <row r="334" spans="1:5">
       <c r="A334" s="12" t="s">
-        <v>62</v>
+        <v>451</v>
       </c>
       <c r="B334" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C334" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D334" s="12" t="s">
         <v>365</v>
@@ -12597,10 +12579,10 @@
     </row>
     <row r="335" spans="1:5">
       <c r="A335" s="12" t="s">
-        <v>65</v>
+        <v>452</v>
       </c>
       <c r="B335" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C335" s="12" t="s">
         <v>247</v>
@@ -12614,13 +12596,13 @@
     </row>
     <row r="336" spans="1:5">
       <c r="A336" s="12" t="s">
-        <v>65</v>
+        <v>453</v>
       </c>
       <c r="B336" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C336" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D336" s="12" t="s">
         <v>365</v>
@@ -12631,10 +12613,10 @@
     </row>
     <row r="337" spans="1:5">
       <c r="A337" s="12" t="s">
-        <v>67</v>
+        <v>454</v>
       </c>
       <c r="B337" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C337" s="12" t="s">
         <v>247</v>
@@ -12648,13 +12630,13 @@
     </row>
     <row r="338" spans="1:5">
       <c r="A338" s="12" t="s">
-        <v>67</v>
+        <v>462</v>
       </c>
       <c r="B338" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C338" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D338" s="12" t="s">
         <v>365</v>
@@ -12665,13 +12647,13 @@
     </row>
     <row r="339" spans="1:5">
       <c r="A339" s="12" t="s">
-        <v>71</v>
+        <v>579</v>
       </c>
       <c r="B339" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C339" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D339" s="12" t="s">
         <v>365</v>
@@ -12682,10 +12664,10 @@
     </row>
     <row r="340" spans="1:5">
       <c r="A340" s="12" t="s">
-        <v>71</v>
+        <v>583</v>
       </c>
       <c r="B340" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C340" s="12" t="s">
         <v>247</v>
@@ -12699,10 +12681,10 @@
     </row>
     <row r="341" spans="1:5">
       <c r="A341" s="12" t="s">
-        <v>71</v>
+        <v>587</v>
       </c>
       <c r="B341" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C341" s="12" t="s">
         <v>248</v>
@@ -12716,13 +12698,13 @@
     </row>
     <row r="342" spans="1:5">
       <c r="A342" s="12" t="s">
-        <v>73</v>
+        <v>619</v>
       </c>
       <c r="B342" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C342" s="12" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D342" s="12" t="s">
         <v>365</v>
@@ -12733,13 +12715,13 @@
     </row>
     <row r="343" spans="1:5">
       <c r="A343" s="12" t="s">
-        <v>78</v>
+        <v>628</v>
       </c>
       <c r="B343" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C343" s="12" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D343" s="12" t="s">
         <v>365</v>
@@ -12750,13 +12732,13 @@
     </row>
     <row r="344" spans="1:5">
       <c r="A344" s="12" t="s">
-        <v>82</v>
+        <v>636</v>
       </c>
       <c r="B344" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C344" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D344" s="12" t="s">
         <v>365</v>
@@ -12767,716 +12749,716 @@
     </row>
     <row r="345" spans="1:5">
       <c r="A345" s="12" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="B345" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C345" s="12" t="s">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="D345" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E345" s="12" t="s">
-        <v>364</v>
+        <v>798</v>
       </c>
     </row>
     <row r="346" spans="1:5">
       <c r="A346" s="12" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="B346" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C346" s="12" t="s">
-        <v>249</v>
+        <v>27</v>
       </c>
       <c r="D346" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E346" s="12" t="s">
-        <v>364</v>
+        <v>798</v>
       </c>
     </row>
     <row r="347" spans="1:5">
       <c r="A347" s="12" t="s">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="B347" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C347" s="12" t="s">
-        <v>243</v>
+        <v>34</v>
       </c>
       <c r="D347" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E347" s="12" t="s">
-        <v>364</v>
+        <v>799</v>
       </c>
     </row>
     <row r="348" spans="1:5">
       <c r="A348" s="12" t="s">
-        <v>260</v>
+        <v>10</v>
       </c>
       <c r="B348" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C348" s="12" t="s">
-        <v>244</v>
+        <v>40</v>
       </c>
       <c r="D348" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E348" s="12" t="s">
-        <v>364</v>
+        <v>800</v>
       </c>
     </row>
     <row r="349" spans="1:5">
       <c r="A349" s="12" t="s">
-        <v>268</v>
+        <v>10</v>
       </c>
       <c r="B349" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C349" s="12" t="s">
-        <v>244</v>
+        <v>46</v>
       </c>
       <c r="D349" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E349" s="12" t="s">
-        <v>364</v>
+        <v>798</v>
       </c>
     </row>
     <row r="350" spans="1:5">
       <c r="A350" s="12" t="s">
-        <v>268</v>
+        <v>10</v>
       </c>
       <c r="B350" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C350" s="12" t="s">
-        <v>245</v>
+        <v>50</v>
       </c>
       <c r="D350" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E350" s="12" t="s">
-        <v>364</v>
+        <v>798</v>
       </c>
     </row>
     <row r="351" spans="1:5">
       <c r="A351" s="12" t="s">
-        <v>275</v>
+        <v>10</v>
       </c>
       <c r="B351" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C351" s="12" t="s">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="D351" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E351" s="12" t="s">
-        <v>364</v>
+        <v>798</v>
       </c>
     </row>
     <row r="352" spans="1:5">
       <c r="A352" s="12" t="s">
-        <v>286</v>
+        <v>10</v>
       </c>
       <c r="B352" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C352" s="12" t="s">
-        <v>245</v>
+        <v>560</v>
       </c>
       <c r="D352" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E352" s="12" t="s">
-        <v>364</v>
+        <v>798</v>
       </c>
     </row>
     <row r="353" spans="1:5">
       <c r="A353" s="12" t="s">
-        <v>297</v>
+        <v>20</v>
       </c>
       <c r="B353" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C353" s="12" t="s">
-        <v>246</v>
+        <v>50</v>
       </c>
       <c r="D353" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E353" s="12" t="s">
-        <v>364</v>
+        <v>801</v>
       </c>
     </row>
     <row r="354" spans="1:5">
       <c r="A354" s="12" t="s">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="B354" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C354" s="12" t="s">
-        <v>246</v>
+        <v>418</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E354" s="12" t="s">
-        <v>364</v>
+        <v>802</v>
       </c>
     </row>
     <row r="355" spans="1:5">
       <c r="A355" s="12" t="s">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="B355" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C355" s="12" t="s">
-        <v>247</v>
+        <v>419</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E355" s="12" t="s">
-        <v>364</v>
+        <v>802</v>
       </c>
     </row>
     <row r="356" spans="1:5">
       <c r="A356" s="12" t="s">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="B356" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C356" s="12" t="s">
-        <v>248</v>
+        <v>420</v>
       </c>
       <c r="D356" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E356" s="12" t="s">
-        <v>364</v>
+        <v>802</v>
       </c>
     </row>
     <row r="357" spans="1:5">
       <c r="A357" s="12" t="s">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="B357" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C357" s="12" t="s">
-        <v>249</v>
+        <v>421</v>
       </c>
       <c r="D357" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E357" s="12" t="s">
-        <v>364</v>
+        <v>530</v>
       </c>
     </row>
     <row r="358" spans="1:5">
       <c r="A358" s="12" t="s">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="B358" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C358" s="12" t="s">
-        <v>247</v>
+        <v>422</v>
       </c>
       <c r="D358" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E358" s="12" t="s">
-        <v>364</v>
+        <v>803</v>
       </c>
     </row>
     <row r="359" spans="1:5">
       <c r="A359" s="12" t="s">
-        <v>419</v>
+        <v>27</v>
       </c>
       <c r="B359" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C359" s="12" t="s">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="D359" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E359" s="12" t="s">
-        <v>364</v>
+        <v>804</v>
       </c>
     </row>
     <row r="360" spans="1:5">
       <c r="A360" s="12" t="s">
-        <v>420</v>
+        <v>34</v>
       </c>
       <c r="B360" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C360" s="12" t="s">
-        <v>247</v>
+        <v>10</v>
       </c>
       <c r="D360" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E360" s="12" t="s">
-        <v>364</v>
+        <v>805</v>
       </c>
     </row>
     <row r="361" spans="1:5">
       <c r="A361" s="12" t="s">
-        <v>421</v>
+        <v>40</v>
       </c>
       <c r="B361" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C361" s="12" t="s">
-        <v>247</v>
+        <v>10</v>
       </c>
       <c r="D361" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E361" s="12" t="s">
-        <v>364</v>
+        <v>806</v>
       </c>
     </row>
     <row r="362" spans="1:5">
       <c r="A362" s="12" t="s">
-        <v>422</v>
+        <v>50</v>
       </c>
       <c r="B362" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C362" s="12" t="s">
-        <v>247</v>
+        <v>20</v>
       </c>
       <c r="D362" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E362" s="12" t="s">
-        <v>364</v>
+        <v>807</v>
       </c>
     </row>
     <row r="363" spans="1:5">
       <c r="A363" s="12" t="s">
-        <v>423</v>
+        <v>54</v>
       </c>
       <c r="B363" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C363" s="12" t="s">
-        <v>246</v>
+        <v>67</v>
       </c>
       <c r="D363" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E363" s="12" t="s">
-        <v>364</v>
+        <v>808</v>
       </c>
     </row>
     <row r="364" spans="1:5">
       <c r="A364" s="12" t="s">
-        <v>423</v>
+        <v>54</v>
       </c>
       <c r="B364" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C364" s="12" t="s">
-        <v>247</v>
+        <v>71</v>
       </c>
       <c r="D364" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E364" s="12" t="s">
-        <v>364</v>
+        <v>808</v>
       </c>
     </row>
     <row r="365" spans="1:5">
       <c r="A365" s="12" t="s">
-        <v>560</v>
+        <v>54</v>
       </c>
       <c r="B365" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C365" s="12" t="s">
-        <v>247</v>
+        <v>423</v>
       </c>
       <c r="D365" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E365" s="12" t="s">
-        <v>364</v>
+        <v>809</v>
       </c>
     </row>
     <row r="366" spans="1:5">
       <c r="A366" s="12" t="s">
-        <v>560</v>
+        <v>62</v>
       </c>
       <c r="B366" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C366" s="12" t="s">
-        <v>248</v>
+        <v>54</v>
       </c>
       <c r="D366" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E366" s="12" t="s">
-        <v>364</v>
+        <v>811</v>
       </c>
     </row>
     <row r="367" spans="1:5">
       <c r="A367" s="12" t="s">
-        <v>560</v>
+        <v>62</v>
       </c>
       <c r="B367" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C367" s="12" t="s">
-        <v>249</v>
+        <v>67</v>
       </c>
       <c r="D367" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E367" s="12" t="s">
-        <v>364</v>
+        <v>798</v>
       </c>
     </row>
     <row r="368" spans="1:5">
       <c r="A368" s="12" t="s">
-        <v>567</v>
+        <v>62</v>
       </c>
       <c r="B368" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C368" s="12" t="s">
-        <v>247</v>
+        <v>73</v>
       </c>
       <c r="D368" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E368" s="12" t="s">
-        <v>364</v>
+        <v>810</v>
       </c>
     </row>
     <row r="369" spans="1:5">
       <c r="A369" s="12" t="s">
-        <v>574</v>
+        <v>65</v>
       </c>
       <c r="B369" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C369" s="12" t="s">
-        <v>248</v>
+        <v>54</v>
       </c>
       <c r="D369" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E369" s="12" t="s">
-        <v>364</v>
+        <v>811</v>
       </c>
     </row>
     <row r="370" spans="1:5">
       <c r="A370" s="12" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="B370" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C370" s="12" t="s">
-        <v>247</v>
+        <v>62</v>
       </c>
       <c r="D370" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E370" s="12" t="s">
-        <v>364</v>
+        <v>812</v>
       </c>
     </row>
     <row r="371" spans="1:5">
       <c r="A371" s="12" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="B371" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C371" s="12" t="s">
-        <v>248</v>
+        <v>54</v>
       </c>
       <c r="D371" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E371" s="12" t="s">
-        <v>364</v>
+        <v>813</v>
       </c>
     </row>
     <row r="372" spans="1:5">
       <c r="A372" s="12" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B372" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C372" s="12" t="s">
-        <v>248</v>
+        <v>54</v>
       </c>
       <c r="D372" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E372" s="12" t="s">
-        <v>364</v>
+        <v>814</v>
       </c>
     </row>
     <row r="373" spans="1:5">
       <c r="A373" s="12" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B373" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C373" s="12" t="s">
-        <v>248</v>
+        <v>62</v>
       </c>
       <c r="D373" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E373" s="12" t="s">
-        <v>364</v>
+        <v>815</v>
       </c>
     </row>
     <row r="374" spans="1:5">
       <c r="A374" s="12" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="B374" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C374" s="12" t="s">
-        <v>248</v>
+        <v>65</v>
       </c>
       <c r="D374" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E374" s="12" t="s">
-        <v>364</v>
+        <v>816</v>
       </c>
     </row>
     <row r="375" spans="1:5">
       <c r="A375" s="12" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="B375" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C375" s="12" t="s">
-        <v>248</v>
+        <v>65</v>
       </c>
       <c r="D375" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E375" s="12" t="s">
-        <v>364</v>
+        <v>799</v>
       </c>
     </row>
     <row r="376" spans="1:5">
       <c r="A376" s="12" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="B376" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C376" s="12" t="s">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="D376" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E376" s="12" t="s">
-        <v>364</v>
+        <v>798</v>
       </c>
     </row>
     <row r="377" spans="1:5">
       <c r="A377" s="12" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="B377" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C377" s="12" t="s">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="D377" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E377" s="12" t="s">
-        <v>364</v>
+        <v>817</v>
       </c>
     </row>
     <row r="378" spans="1:5">
       <c r="A378" s="12" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="B378" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C378" s="12" t="s">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="D378" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E378" s="12" t="s">
-        <v>364</v>
+        <v>817</v>
       </c>
     </row>
     <row r="379" spans="1:5">
       <c r="A379" s="12" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="B379" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C379" s="12" t="s">
-        <v>248</v>
+        <v>73</v>
       </c>
       <c r="D379" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E379" s="12" t="s">
-        <v>364</v>
+        <v>817</v>
       </c>
     </row>
     <row r="380" spans="1:5">
       <c r="A380" s="12" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="B380" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C380" s="12" t="s">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="D380" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E380" s="12" t="s">
-        <v>364</v>
+        <v>817</v>
       </c>
     </row>
     <row r="381" spans="1:5">
       <c r="A381" s="12" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="B381" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C381" s="12" t="s">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="D381" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E381" s="12" t="s">
-        <v>364</v>
+        <v>806</v>
       </c>
     </row>
     <row r="382" spans="1:5">
       <c r="A382" s="12" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="B382" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C382" s="12" t="s">
-        <v>243</v>
+        <v>10</v>
       </c>
       <c r="D382" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E382" s="12" t="s">
-        <v>364</v>
+        <v>818</v>
       </c>
     </row>
     <row r="383" spans="1:5">
       <c r="A383" s="12" t="s">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="B383" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C383" s="12" t="s">
-        <v>244</v>
+        <v>27</v>
       </c>
       <c r="D383" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E383" s="12" t="s">
-        <v>364</v>
+        <v>819</v>
       </c>
     </row>
     <row r="384" spans="1:5">
       <c r="A384" s="12" t="s">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="B384" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C384" s="12" t="s">
-        <v>245</v>
+        <v>40</v>
       </c>
       <c r="D384" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E384" s="12" t="s">
-        <v>364</v>
+        <v>819</v>
       </c>
     </row>
     <row r="385" spans="1:5">
       <c r="A385" s="12" t="s">
-        <v>347</v>
+        <v>423</v>
       </c>
       <c r="B385" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C385" s="12" t="s">
-        <v>246</v>
+        <v>54</v>
       </c>
       <c r="D385" s="12" t="s">
-        <v>365</v>
+        <v>158</v>
       </c>
       <c r="E385" s="12" t="s">
-        <v>364</v>
+        <v>820</v>
       </c>
     </row>
     <row r="386" spans="1:5">
       <c r="A386" s="12" t="s">
-        <v>350</v>
+        <v>454</v>
       </c>
       <c r="B386" s="12" t="s">
         <v>159</v>
       </c>
       <c r="C386" s="12" t="s">
-        <v>249</v>
+        <v>92</v>
       </c>
       <c r="D386" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E386" s="12" t="s">
-        <v>364</v>
+        <v>527</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -13487,1679 +13469,251 @@
         <v>159</v>
       </c>
       <c r="C387" s="12" t="s">
-        <v>247</v>
+        <v>785</v>
       </c>
       <c r="D387" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E387" s="12" t="s">
-        <v>364</v>
+        <v>832</v>
       </c>
     </row>
     <row r="388" spans="1:5">
       <c r="A388" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="B388" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C388" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="B388" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C388" s="12" t="s">
-        <v>247</v>
-      </c>
       <c r="D388" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E388" s="12" t="s">
-        <v>364</v>
+        <v>832</v>
       </c>
     </row>
     <row r="389" spans="1:5">
       <c r="A389" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="B389" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C389" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="B389" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C389" s="12" t="s">
-        <v>247</v>
-      </c>
       <c r="D389" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E389" s="12" t="s">
-        <v>364</v>
+        <v>528</v>
       </c>
     </row>
     <row r="390" spans="1:5">
       <c r="A390" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="B390" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C390" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="B390" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C390" s="12" t="s">
-        <v>247</v>
-      </c>
       <c r="D390" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E390" s="12" t="s">
-        <v>364</v>
+        <v>527</v>
       </c>
     </row>
     <row r="391" spans="1:5">
       <c r="A391" s="12" t="s">
-        <v>462</v>
+        <v>109</v>
       </c>
       <c r="B391" s="12" t="s">
         <v>159</v>
       </c>
       <c r="C391" s="12" t="s">
-        <v>247</v>
+        <v>111</v>
       </c>
       <c r="D391" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E391" s="12" t="s">
-        <v>364</v>
+        <v>527</v>
       </c>
     </row>
     <row r="392" spans="1:5">
       <c r="A392" s="12" t="s">
-        <v>579</v>
+        <v>111</v>
       </c>
       <c r="B392" s="12" t="s">
         <v>159</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>247</v>
+        <v>112</v>
       </c>
       <c r="D392" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E392" s="12" t="s">
-        <v>364</v>
+        <v>528</v>
       </c>
     </row>
     <row r="393" spans="1:5">
       <c r="A393" s="12" t="s">
-        <v>583</v>
+        <v>94</v>
       </c>
       <c r="B393" s="12" t="s">
         <v>159</v>
       </c>
       <c r="C393" s="12" t="s">
-        <v>247</v>
+        <v>102</v>
       </c>
       <c r="D393" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E393" s="12" t="s">
-        <v>364</v>
+        <v>528</v>
       </c>
     </row>
     <row r="394" spans="1:5">
       <c r="A394" s="12" t="s">
-        <v>587</v>
+        <v>96</v>
       </c>
       <c r="B394" s="12" t="s">
         <v>159</v>
       </c>
       <c r="C394" s="12" t="s">
-        <v>248</v>
+        <v>98</v>
       </c>
       <c r="D394" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E394" s="12" t="s">
-        <v>364</v>
+        <v>527</v>
       </c>
     </row>
     <row r="395" spans="1:5">
       <c r="A395" s="12" t="s">
-        <v>619</v>
+        <v>102</v>
       </c>
       <c r="B395" s="12" t="s">
         <v>159</v>
       </c>
       <c r="C395" s="12" t="s">
-        <v>244</v>
+        <v>98</v>
       </c>
       <c r="D395" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E395" s="12" t="s">
-        <v>364</v>
+        <v>527</v>
       </c>
     </row>
     <row r="396" spans="1:5">
       <c r="A396" s="12" t="s">
-        <v>628</v>
+        <v>103</v>
       </c>
       <c r="B396" s="12" t="s">
         <v>159</v>
       </c>
       <c r="C396" s="12" t="s">
-        <v>245</v>
+        <v>96</v>
       </c>
       <c r="D396" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E396" s="12" t="s">
-        <v>364</v>
+        <v>821</v>
       </c>
     </row>
     <row r="397" spans="1:5">
       <c r="A397" s="12" t="s">
-        <v>636</v>
+        <v>105</v>
       </c>
       <c r="B397" s="12" t="s">
         <v>159</v>
       </c>
       <c r="C397" s="12" t="s">
-        <v>246</v>
+        <v>98</v>
       </c>
       <c r="D397" s="12" t="s">
-        <v>365</v>
+        <v>159</v>
       </c>
       <c r="E397" s="12" t="s">
-        <v>364</v>
+        <v>527</v>
       </c>
     </row>
     <row r="398" spans="1:5">
       <c r="A398" s="12" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="B398" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C398" s="12" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="D398" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E398" s="12" t="s">
-        <v>798</v>
+        <v>527</v>
       </c>
     </row>
     <row r="399" spans="1:5">
       <c r="A399" s="12" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="B399" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C399" s="12" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="D399" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E399" s="12" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="400" spans="1:5" ht="27.6">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
       <c r="A400" s="12" t="s">
-        <v>10</v>
+        <v>347</v>
       </c>
       <c r="B400" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C400" s="12" t="s">
-        <v>34</v>
+        <v>451</v>
       </c>
       <c r="D400" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E400" s="12" t="s">
-        <v>799</v>
+        <v>528</v>
       </c>
     </row>
     <row r="401" spans="1:5">
       <c r="A401" s="12" t="s">
-        <v>10</v>
+        <v>462</v>
       </c>
       <c r="B401" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C401" s="12" t="s">
-        <v>40</v>
+        <v>347</v>
       </c>
       <c r="D401" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E401" s="12" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="402" spans="1:5">
-      <c r="A402" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B402" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C402" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D402" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E402" s="12" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="403" spans="1:5">
-      <c r="A403" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B403" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C403" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D403" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E403" s="12" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="404" spans="1:5">
-      <c r="A404" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B404" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C404" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D404" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E404" s="12" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="405" spans="1:5">
-      <c r="A405" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B405" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C405" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="D405" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E405" s="12" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="406" spans="1:5">
-      <c r="A406" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B406" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C406" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D406" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E406" s="12" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="407" spans="1:5">
-      <c r="A407" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B407" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C407" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D407" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E407" s="12" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="408" spans="1:5">
-      <c r="A408" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B408" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C408" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="D408" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E408" s="12" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="409" spans="1:5">
-      <c r="A409" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B409" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C409" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="D409" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E409" s="12" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="410" spans="1:5">
-      <c r="A410" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B410" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C410" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="D410" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E410" s="12" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="411" spans="1:5">
-      <c r="A411" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B411" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C411" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="D411" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E411" s="12" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="412" spans="1:5">
-      <c r="A412" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B412" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C412" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="D412" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E412" s="12" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="413" spans="1:5">
-      <c r="A413" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B413" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C413" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D413" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E413" s="12" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="414" spans="1:5">
-      <c r="A414" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B414" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C414" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D414" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E414" s="12" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="415" spans="1:5">
-      <c r="A415" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B415" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C415" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D415" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E415" s="12" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="416" spans="1:5">
-      <c r="A416" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B416" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C416" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D416" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E416" s="12" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5">
-      <c r="A417" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B417" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C417" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D417" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E417" s="12" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="418" spans="1:5" ht="27.6">
-      <c r="A418" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B418" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C418" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D418" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E418" s="12" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="419" spans="1:5">
-      <c r="A419" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B419" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C419" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D419" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E419" s="12" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="420" spans="1:5">
-      <c r="A420" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B420" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C420" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D420" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E420" s="12" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="421" spans="1:5">
-      <c r="A421" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B421" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C421" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D421" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E421" s="12" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="422" spans="1:5">
-      <c r="A422" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B422" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C422" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D422" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E422" s="12" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="423" spans="1:5">
-      <c r="A423" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B423" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C423" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="D423" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E423" s="12" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="424" spans="1:5">
-      <c r="A424" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B424" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C424" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D424" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E424" s="12" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="425" spans="1:5">
-      <c r="A425" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B425" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C425" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D425" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E425" s="12" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="426" spans="1:5">
-      <c r="A426" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B426" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C426" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D426" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E426" s="12" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="427" spans="1:5">
-      <c r="A427" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B427" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C427" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D427" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E427" s="12" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="428" spans="1:5">
-      <c r="A428" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B428" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C428" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D428" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E428" s="12" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="429" spans="1:5">
-      <c r="A429" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B429" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C429" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D429" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E429" s="12" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="430" spans="1:5">
-      <c r="A430" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B430" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C430" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D430" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E430" s="12" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="431" spans="1:5">
-      <c r="A431" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B431" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C431" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D431" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E431" s="12" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="432" spans="1:5">
-      <c r="A432" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B432" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C432" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D432" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E432" s="12" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="433" spans="1:5">
-      <c r="A433" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B433" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C433" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D433" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E433" s="12" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="434" spans="1:5">
-      <c r="A434" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B434" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C434" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D434" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E434" s="12" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="435" spans="1:5">
-      <c r="A435" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B435" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C435" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D435" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E435" s="12" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="436" spans="1:5">
-      <c r="A436" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B436" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C436" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D436" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E436" s="12" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="437" spans="1:5">
-      <c r="A437" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B437" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C437" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D437" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E437" s="12" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="438" spans="1:5">
-      <c r="A438" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B438" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C438" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D438" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E438" s="12" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="439" spans="1:5">
-      <c r="A439" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B439" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C439" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D439" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E439" s="12" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="440" spans="1:5">
-      <c r="A440" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B440" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C440" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D440" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E440" s="12" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="441" spans="1:5">
-      <c r="A441" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B441" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C441" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D441" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E441" s="12" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="442" spans="1:5">
-      <c r="A442" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="B442" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C442" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D442" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E442" s="12" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="443" spans="1:5">
-      <c r="A443" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="B443" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C443" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D443" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E443" s="12" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="444" spans="1:5">
-      <c r="A444" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="B444" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C444" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D444" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E444" s="12" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="445" spans="1:5">
-      <c r="A445" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="B445" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C445" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D445" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E445" s="12" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="446" spans="1:5">
-      <c r="A446" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="B446" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C446" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D446" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E446" s="12" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="447" spans="1:5">
-      <c r="A447" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="B447" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C447" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D447" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E447" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="448" spans="1:5">
-      <c r="A448" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="B448" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C448" s="12" t="s">
-        <v>619</v>
-      </c>
-      <c r="D448" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E448" s="12" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="449" spans="1:5">
-      <c r="A449" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B449" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C449" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D449" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E449" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="450" spans="1:5">
-      <c r="A450" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="B450" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C450" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="D450" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E450" s="12" t="s">
         <v>480</v>
-      </c>
-    </row>
-    <row r="451" spans="1:5">
-      <c r="A451" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="B451" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C451" s="12" t="s">
-        <v>785</v>
-      </c>
-      <c r="D451" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E451" s="12" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="452" spans="1:5">
-      <c r="A452" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="B452" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C452" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="D452" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E452" s="12" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="453" spans="1:5">
-      <c r="A453" s="12" t="s">
-        <v>785</v>
-      </c>
-      <c r="B453" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C453" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="D453" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E453" s="12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="454" spans="1:5">
-      <c r="A454" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="B454" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C454" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="D454" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E454" s="12" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="455" spans="1:5">
-      <c r="A455" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="B455" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C455" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="D455" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E455" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="456" spans="1:5">
-      <c r="A456" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="B456" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C456" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="D456" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E456" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="457" spans="1:5">
-      <c r="A457" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B457" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C457" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D457" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E457" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="458" spans="1:5">
-      <c r="A458" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B458" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C458" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D458" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E458" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="459" spans="1:5">
-      <c r="A459" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B459" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C459" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D459" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E459" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="460" spans="1:5">
-      <c r="A460" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B460" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C460" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D460" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E460" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="461" spans="1:5">
-      <c r="A461" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B461" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C461" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D461" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E461" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="462" spans="1:5">
-      <c r="A462" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B462" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C462" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D462" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E462" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="463" spans="1:5">
-      <c r="A463" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B463" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C463" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D463" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E463" s="12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="464" spans="1:5">
-      <c r="A464" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B464" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C464" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D464" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E464" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="465" spans="1:5">
-      <c r="A465" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B465" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C465" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D465" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E465" s="12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="466" spans="1:5">
-      <c r="A466" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B466" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C466" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D466" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E466" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="467" spans="1:5">
-      <c r="A467" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B467" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C467" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D467" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E467" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="468" spans="1:5">
-      <c r="A468" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B468" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C468" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D468" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E468" s="12" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="469" spans="1:5">
-      <c r="A469" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="B469" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C469" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="D469" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E469" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="470" spans="1:5">
-      <c r="A470" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="B470" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C470" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="D470" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E470" s="12" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="471" spans="1:5">
-      <c r="A471" s="12" t="s">
-        <v>619</v>
-      </c>
-      <c r="B471" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C471" s="12" t="s">
-        <v>628</v>
-      </c>
-      <c r="D471" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E471" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="472" spans="1:5">
-      <c r="A472" s="12" t="s">
-        <v>628</v>
-      </c>
-      <c r="B472" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C472" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="D472" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E472" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="473" spans="1:5">
-      <c r="A473" s="12" t="s">
-        <v>636</v>
-      </c>
-      <c r="B473" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C473" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="D473" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E473" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="474" spans="1:5">
-      <c r="A474" s="12" t="s">
-        <v>785</v>
-      </c>
-      <c r="B474" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C474" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="D474" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E474" s="12" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="475" spans="1:5">
-      <c r="A475" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="B475" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C475" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="D475" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E475" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="476" spans="1:5">
-      <c r="A476" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="B476" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C476" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="D476" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E476" s="12" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="477" spans="1:5">
-      <c r="A477" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="B477" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C477" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="D477" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E477" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="478" spans="1:5">
-      <c r="A478" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="B478" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C478" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="D478" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E478" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="479" spans="1:5">
-      <c r="A479" s="12" t="s">
-        <v>587</v>
-      </c>
-      <c r="B479" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C479" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D479" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E479" s="12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="480" spans="1:5">
-      <c r="A480" s="12" t="s">
-        <v>583</v>
-      </c>
-      <c r="B480" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C480" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D480" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E480" s="12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="481" spans="1:5">
-      <c r="A481" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="B481" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C481" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="D481" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E481" s="12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="482" spans="1:5">
-      <c r="A482" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="B482" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C482" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="D482" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E482" s="12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="483" spans="1:5">
-      <c r="A483" s="12" t="s">
-        <v>579</v>
-      </c>
-      <c r="B483" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C483" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="D483" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E483" s="12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="484" spans="1:5">
-      <c r="A484" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B484" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C484" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D484" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E484" s="12" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="485" spans="1:5">
-      <c r="A485" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="B485" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="C485" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D485" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E485" s="12" t="s">
-        <v>527</v>
       </c>
     </row>
   </sheetData>
